--- a/CLASS/SS3/English_language/results.xlsx
+++ b/CLASS/SS3/English_language/results.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,43 +466,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Abubakar Fatima Shehu</t>
+          <t>Bello Muhammad Abba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>std356</t>
+          <t>std396</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>SS3_B</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ENGLISH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>80</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-12-07 20:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Soje Halima AbdulJabar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>std366</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>SS3_GOLD</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ENGLISH LANGUAGE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>76</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ENGLISH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2025-12-04 07:30</t>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-12-08 00:13</t>
         </is>
       </c>
     </row>
